--- a/CASA ROSSA Ale Nuovi movimenti.xlsx
+++ b/CASA ROSSA Ale Nuovi movimenti.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15132" yWindow="5016" windowWidth="27132" windowHeight="17760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-4524" yWindow="-26028" windowWidth="46296" windowHeight="25416" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Scheda Movimenti" sheetId="1" state="visible" r:id="rId1"/>
@@ -1107,23 +1107,23 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O138"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="15.59765625" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="15.58203125" defaultRowHeight="15.5"/>
   <cols>
-    <col width="10.19921875" customWidth="1" style="1" min="1" max="1"/>
-    <col width="11.3984375" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
-    <col width="6.8984375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8.296875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="10.1640625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="11.4140625" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="6.9140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8.33203125" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
     <col width="9.5" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
-    <col width="38.8984375" customWidth="1" min="6" max="6"/>
-    <col width="50.19921875" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="15.296875" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="10.19921875" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="8.296875" bestFit="1" customWidth="1" style="4" min="10" max="10"/>
-    <col width="10.09765625" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="12.19921875" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="38.9140625" customWidth="1" min="6" max="6"/>
+    <col width="50.1640625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="15.33203125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="10.1640625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="8.33203125" bestFit="1" customWidth="1" style="4" min="10" max="10"/>
+    <col width="10.08203125" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="12.1640625" bestFit="1" customWidth="1" min="12" max="12"/>
     <col width="9" bestFit="1" customWidth="1" min="13" max="13"/>
     <col width="18.5" bestFit="1" customWidth="1" min="14" max="14"/>
-    <col width="17.8984375" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="17.9140625" bestFit="1" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1570,11 +1570,7 @@
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>AB002</t>
-        </is>
-      </c>
+      <c r="A8" s="13" t="inlineStr"/>
       <c r="B8" s="13" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -1741,11 +1737,7 @@
       <c r="O10" s="13" t="inlineStr"/>
     </row>
     <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>SM004</t>
-        </is>
-      </c>
+      <c r="A11" s="13" t="inlineStr"/>
       <c r="B11" s="13" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -1798,11 +1790,7 @@
       <c r="O11" s="13" t="inlineStr"/>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>SP006</t>
-        </is>
-      </c>
+      <c r="A12" s="13" t="inlineStr"/>
       <c r="B12" s="13" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -1857,7 +1845,7 @@
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>CA004</t>
+          <t>SP006</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -1912,11 +1900,7 @@
       <c r="O13" s="13" t="inlineStr"/>
     </row>
     <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>SC002</t>
-        </is>
-      </c>
+      <c r="A14" s="13" t="inlineStr"/>
       <c r="B14" s="13" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -2125,7 +2109,11 @@
       <c r="L17" s="13" t="inlineStr"/>
       <c r="M17" s="13" t="inlineStr"/>
       <c r="N17" s="13" t="inlineStr"/>
-      <c r="O17" s="13" t="inlineStr"/>
+      <c r="O17" s="13" t="inlineStr">
+        <is>
+          <t>Manuale (Suggerito)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="27" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
@@ -2192,7 +2180,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="40.2" customHeight="1">
+    <row r="19" ht="40.25" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
           <t>BA004</t>
@@ -2376,11 +2364,7 @@
       </c>
     </row>
     <row r="22" ht="53.4" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>CA008</t>
-        </is>
-      </c>
+      <c r="A22" s="13" t="inlineStr"/>
       <c r="B22" s="13" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -2550,7 +2534,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="40.2" customHeight="1">
+    <row r="25" ht="40.25" customHeight="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
           <t>SP005</t>
@@ -2660,7 +2644,7 @@
       <c r="N26" s="13" t="inlineStr"/>
       <c r="O26" s="13" t="inlineStr"/>
     </row>
-    <row r="27" ht="40.2" customHeight="1">
+    <row r="27" ht="40.25" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
           <t>VA902</t>
@@ -2839,7 +2823,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="40.2" customHeight="1">
+    <row r="30" ht="40.25" customHeight="1">
       <c r="A30" s="13" t="inlineStr"/>
       <c r="B30" s="13" t="inlineStr">
         <is>
@@ -3377,7 +3361,7 @@
       <c r="N39" s="13" t="inlineStr"/>
       <c r="O39" s="13" t="inlineStr"/>
     </row>
-    <row r="40" ht="40.2" customHeight="1">
+    <row r="40" ht="40.25" customHeight="1">
       <c r="A40" s="13" t="inlineStr"/>
       <c r="B40" s="13" t="inlineStr">
         <is>
@@ -3703,7 +3687,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="40.2" customHeight="1">
+    <row r="46" ht="40.25" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
           <t>BA004</t>
@@ -3959,7 +3943,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="40.2" customHeight="1">
+    <row r="50" ht="40.25" customHeight="1">
       <c r="A50" s="13" t="inlineStr">
         <is>
           <t>TA002</t>
@@ -4342,7 +4326,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="40.2" customHeight="1">
+    <row r="57" ht="40.25" customHeight="1">
       <c r="A57" s="13" t="inlineStr">
         <is>
           <t>SP006</t>
@@ -4448,7 +4432,7 @@
       <c r="N58" s="13" t="inlineStr"/>
       <c r="O58" s="13" t="inlineStr"/>
     </row>
-    <row r="59" ht="40.2" customHeight="1">
+    <row r="59" ht="40.25" customHeight="1">
       <c r="A59" s="13" t="inlineStr"/>
       <c r="B59" s="13" t="inlineStr">
         <is>
@@ -4912,7 +4896,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="40.2" customHeight="1">
+    <row r="67" ht="40.25" customHeight="1">
       <c r="A67" s="13" t="inlineStr"/>
       <c r="B67" s="13" t="inlineStr">
         <is>
@@ -5022,7 +5006,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="40.2" customHeight="1">
+    <row r="69" ht="40.25" customHeight="1">
       <c r="A69" s="13" t="inlineStr">
         <is>
           <t>TR013</t>
@@ -5148,7 +5132,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="40.2" customHeight="1">
+    <row r="71" ht="40.25" customHeight="1">
       <c r="A71" s="13" t="inlineStr"/>
       <c r="B71" s="13" t="inlineStr">
         <is>
@@ -5197,7 +5181,7 @@
       <c r="N71" s="13" t="inlineStr"/>
       <c r="O71" s="13" t="inlineStr"/>
     </row>
-    <row r="72" ht="40.2" customHeight="1">
+    <row r="72" ht="40.25" customHeight="1">
       <c r="A72" s="13" t="inlineStr"/>
       <c r="B72" s="13" t="inlineStr">
         <is>
@@ -5315,7 +5299,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="40.2" customHeight="1">
+    <row r="74" ht="40.25" customHeight="1">
       <c r="A74" s="13" t="inlineStr"/>
       <c r="B74" s="13" t="inlineStr">
         <is>
@@ -5718,7 +5702,7 @@
       <c r="N80" s="13" t="inlineStr"/>
       <c r="O80" s="13" t="inlineStr"/>
     </row>
-    <row r="81" ht="40.2" customHeight="1">
+    <row r="81" ht="40.25" customHeight="1">
       <c r="A81" s="13" t="inlineStr"/>
       <c r="B81" s="13" t="inlineStr">
         <is>
@@ -6455,7 +6439,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="40.2" customHeight="1">
+    <row r="94" ht="40.25" customHeight="1">
       <c r="A94" s="13" t="inlineStr"/>
       <c r="B94" s="13" t="inlineStr">
         <is>
@@ -6916,7 +6900,7 @@
       <c r="N102" s="13" t="inlineStr"/>
       <c r="O102" s="13" t="inlineStr"/>
     </row>
-    <row r="103" ht="40.2" customHeight="1">
+    <row r="103" ht="40.25" customHeight="1">
       <c r="A103" s="13" t="inlineStr">
         <is>
           <t>SM003</t>
@@ -7136,7 +7120,7 @@
       <c r="N106" s="13" t="inlineStr"/>
       <c r="O106" s="13" t="inlineStr"/>
     </row>
-    <row r="107" ht="40.2" customHeight="1">
+    <row r="107" ht="40.25" customHeight="1">
       <c r="A107" s="13" t="inlineStr"/>
       <c r="B107" s="13" t="inlineStr">
         <is>
@@ -7824,7 +7808,7 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="40.2" customHeight="1">
+    <row r="119" ht="40.25" customHeight="1">
       <c r="A119" s="13" t="inlineStr">
         <is>
           <t>CA010</t>
@@ -7885,7 +7869,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="40.2" customHeight="1">
+    <row r="120" ht="40.25" customHeight="1">
       <c r="A120" s="13" t="inlineStr"/>
       <c r="B120" s="13" t="inlineStr">
         <is>
@@ -8117,7 +8101,7 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="40.2" customHeight="1">
+    <row r="124" ht="40.25" customHeight="1">
       <c r="A124" s="13" t="inlineStr">
         <is>
           <t>SC003</t>
@@ -8418,7 +8402,7 @@
       <c r="N128" s="13" t="inlineStr"/>
       <c r="O128" s="13" t="inlineStr"/>
     </row>
-    <row r="129" ht="40.2" customHeight="1">
+    <row r="129" ht="40.25" customHeight="1">
       <c r="A129" s="13" t="inlineStr"/>
       <c r="B129" s="13" t="inlineStr">
         <is>
@@ -8467,7 +8451,7 @@
       <c r="N129" s="13" t="inlineStr"/>
       <c r="O129" s="13" t="inlineStr"/>
     </row>
-    <row r="130" ht="40.2" customHeight="1">
+    <row r="130" ht="40.25" customHeight="1">
       <c r="A130" s="13" t="inlineStr">
         <is>
           <t>CA009</t>
@@ -8528,7 +8512,7 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="40.2" customHeight="1">
+    <row r="131" ht="40.25" customHeight="1">
       <c r="A131" s="13" t="inlineStr"/>
       <c r="B131" s="13" t="inlineStr">
         <is>
@@ -8752,7 +8736,7 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="40.2" customHeight="1">
+    <row r="135" ht="40.25" customHeight="1">
       <c r="A135" s="13" t="inlineStr"/>
       <c r="B135" s="13" t="inlineStr">
         <is>
@@ -8805,7 +8789,7 @@
       <c r="N135" s="13" t="inlineStr"/>
       <c r="O135" s="13" t="inlineStr"/>
     </row>
-    <row r="136" ht="27.6" customHeight="1">
+    <row r="136" ht="27.65" customHeight="1">
       <c r="A136" s="13" t="inlineStr">
         <is>
           <t>BA001</t>
